--- a/InputData/hydgn/FIoHP/Fuel Intensity of Hydrogen Production.xlsx
+++ b/InputData/hydgn/FIoHP/Fuel Intensity of Hydrogen Production.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Modeling\EPS\US\eps-us\InputData\hydgn\FIoHP\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanOBrien\Models\EPS\US\eps-us\InputData\hydgn\FIoHP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{769FC27A-0F30-47A7-847D-C77CEECA095F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49C1EEAB-915A-4B02-8093-F9033F588F63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32625" yWindow="2040" windowWidth="24900" windowHeight="14490" firstSheet="6" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11235" firstSheet="7" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -36,6 +36,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -43,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="55">
   <si>
     <t>Sources:</t>
   </si>
@@ -208,12 +210,6 @@
   </si>
   <si>
     <t>FIoHP Fuel Intensity of Hydrogen Production</t>
-  </si>
-  <si>
-    <t>green hydrogen</t>
-  </si>
-  <si>
-    <t>low carbon hydrogen</t>
   </si>
 </sst>
 </file>
@@ -598,17 +594,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B30"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="98.7265625" customWidth="1"/>
+    <col min="2" max="2" width="98.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -616,112 +612,112 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B5" s="3">
         <v>2019</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B7" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B10" s="2" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B12" s="3">
         <v>2013</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B14" s="4" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B17" s="2" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B19" s="3">
         <v>2019</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B22" s="4" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
     </row>
   </sheetData>
@@ -740,14 +736,14 @@
   <sheetPr>
     <tabColor theme="8" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:AI13"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:AI11"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="30.1796875" customWidth="1"/>
-    <col min="2" max="2" width="9.453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.140625" customWidth="1"/>
+    <col min="2" max="2" width="9.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>52</v>
       </c>
@@ -854,7 +850,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>42</v>
       </c>
@@ -995,7 +991,7 @@
         <v>1.6949152542372881E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>43</v>
       </c>
@@ -1136,7 +1132,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>44</v>
       </c>
@@ -1277,7 +1273,7 @@
         <v>1.3728813559322033</v>
       </c>
     </row>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>45</v>
       </c>
@@ -1418,7 +1414,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>46</v>
       </c>
@@ -1559,7 +1555,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>47</v>
       </c>
@@ -1700,7 +1696,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>48</v>
       </c>
@@ -1841,7 +1837,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>49</v>
       </c>
@@ -1982,7 +1978,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>50</v>
       </c>
@@ -2123,7 +2119,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>51</v>
       </c>
@@ -2261,220 +2257,6 @@
       </c>
       <c r="AI11" s="12">
         <f>'FIoHP-ng-reforming'!AI11</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>55</v>
-      </c>
-      <c r="B12" s="12">
-        <v>0</v>
-      </c>
-      <c r="C12" s="12">
-        <v>0</v>
-      </c>
-      <c r="D12" s="12">
-        <v>0</v>
-      </c>
-      <c r="E12" s="12">
-        <v>0</v>
-      </c>
-      <c r="F12" s="12">
-        <v>0</v>
-      </c>
-      <c r="G12" s="12">
-        <v>0</v>
-      </c>
-      <c r="H12" s="12">
-        <v>0</v>
-      </c>
-      <c r="I12" s="12">
-        <v>0</v>
-      </c>
-      <c r="J12" s="12">
-        <v>0</v>
-      </c>
-      <c r="K12" s="12">
-        <v>0</v>
-      </c>
-      <c r="L12" s="12">
-        <v>0</v>
-      </c>
-      <c r="M12" s="12">
-        <v>0</v>
-      </c>
-      <c r="N12" s="12">
-        <v>0</v>
-      </c>
-      <c r="O12" s="12">
-        <v>0</v>
-      </c>
-      <c r="P12" s="12">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="12">
-        <v>0</v>
-      </c>
-      <c r="R12" s="12">
-        <v>0</v>
-      </c>
-      <c r="S12" s="12">
-        <v>0</v>
-      </c>
-      <c r="T12" s="12">
-        <v>0</v>
-      </c>
-      <c r="U12" s="12">
-        <v>0</v>
-      </c>
-      <c r="V12" s="12">
-        <v>0</v>
-      </c>
-      <c r="W12" s="12">
-        <v>0</v>
-      </c>
-      <c r="X12" s="12">
-        <v>0</v>
-      </c>
-      <c r="Y12" s="12">
-        <v>0</v>
-      </c>
-      <c r="Z12" s="12">
-        <v>0</v>
-      </c>
-      <c r="AA12" s="12">
-        <v>0</v>
-      </c>
-      <c r="AB12" s="12">
-        <v>0</v>
-      </c>
-      <c r="AC12" s="12">
-        <v>0</v>
-      </c>
-      <c r="AD12" s="12">
-        <v>0</v>
-      </c>
-      <c r="AE12" s="12">
-        <v>0</v>
-      </c>
-      <c r="AF12" s="12">
-        <v>0</v>
-      </c>
-      <c r="AG12" s="12">
-        <v>0</v>
-      </c>
-      <c r="AH12" s="12">
-        <v>0</v>
-      </c>
-      <c r="AI12" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>56</v>
-      </c>
-      <c r="B13" s="12">
-        <v>0</v>
-      </c>
-      <c r="C13" s="12">
-        <v>0</v>
-      </c>
-      <c r="D13" s="12">
-        <v>0</v>
-      </c>
-      <c r="E13" s="12">
-        <v>0</v>
-      </c>
-      <c r="F13" s="12">
-        <v>0</v>
-      </c>
-      <c r="G13" s="12">
-        <v>0</v>
-      </c>
-      <c r="H13" s="12">
-        <v>0</v>
-      </c>
-      <c r="I13" s="12">
-        <v>0</v>
-      </c>
-      <c r="J13" s="12">
-        <v>0</v>
-      </c>
-      <c r="K13" s="12">
-        <v>0</v>
-      </c>
-      <c r="L13" s="12">
-        <v>0</v>
-      </c>
-      <c r="M13" s="12">
-        <v>0</v>
-      </c>
-      <c r="N13" s="12">
-        <v>0</v>
-      </c>
-      <c r="O13" s="12">
-        <v>0</v>
-      </c>
-      <c r="P13" s="12">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="12">
-        <v>0</v>
-      </c>
-      <c r="R13" s="12">
-        <v>0</v>
-      </c>
-      <c r="S13" s="12">
-        <v>0</v>
-      </c>
-      <c r="T13" s="12">
-        <v>0</v>
-      </c>
-      <c r="U13" s="12">
-        <v>0</v>
-      </c>
-      <c r="V13" s="12">
-        <v>0</v>
-      </c>
-      <c r="W13" s="12">
-        <v>0</v>
-      </c>
-      <c r="X13" s="12">
-        <v>0</v>
-      </c>
-      <c r="Y13" s="12">
-        <v>0</v>
-      </c>
-      <c r="Z13" s="12">
-        <v>0</v>
-      </c>
-      <c r="AA13" s="12">
-        <v>0</v>
-      </c>
-      <c r="AB13" s="12">
-        <v>0</v>
-      </c>
-      <c r="AC13" s="12">
-        <v>0</v>
-      </c>
-      <c r="AD13" s="12">
-        <v>0</v>
-      </c>
-      <c r="AE13" s="12">
-        <v>0</v>
-      </c>
-      <c r="AF13" s="12">
-        <v>0</v>
-      </c>
-      <c r="AG13" s="12">
-        <v>0</v>
-      </c>
-      <c r="AH13" s="12">
-        <v>0</v>
-      </c>
-      <c r="AI13" s="12">
         <v>0</v>
       </c>
     </row>
@@ -2486,15 +2268,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:F18"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="3" width="25.453125" customWidth="1"/>
-    <col min="4" max="4" width="11.54296875" customWidth="1"/>
-    <col min="5" max="5" width="10.1796875" customWidth="1"/>
-    <col min="6" max="6" width="14.54296875" customWidth="1"/>
+    <col min="1" max="3" width="25.42578125" customWidth="1"/>
+    <col min="4" max="4" width="11.5703125" customWidth="1"/>
+    <col min="5" max="5" width="10.140625" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="9" t="s">
         <v>11</v>
       </c>
@@ -2514,7 +2296,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="15" thickTop="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -2534,7 +2316,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>14</v>
       </c>
@@ -2551,7 +2333,7 @@
         <v>0.74</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>16</v>
       </c>
@@ -2568,7 +2350,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="8"/>
       <c r="B5" s="8" t="s">
         <v>18</v>
@@ -2586,7 +2368,7 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="15" thickTop="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>2</v>
       </c>
@@ -2606,7 +2388,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>14</v>
       </c>
@@ -2623,7 +2405,7 @@
         <v>0.76</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>16</v>
       </c>
@@ -2640,7 +2422,7 @@
         <v>4.7E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="8"/>
       <c r="B9" s="8" t="s">
         <v>20</v>
@@ -2658,7 +2440,7 @@
         <v>8.9</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="15" thickTop="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -2678,7 +2460,7 @@
         <v>2670</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>14</v>
       </c>
@@ -2695,7 +2477,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>16</v>
       </c>
@@ -2712,7 +2494,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="8"/>
       <c r="B13" s="8" t="s">
         <v>20</v>
@@ -2730,8 +2512,8 @@
         <v>20.2</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="15" thickTop="1" x14ac:dyDescent="0.35"/>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:6" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>22</v>
       </c>
@@ -2745,7 +2527,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>27</v>
       </c>
@@ -2766,14 +2548,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0A8BC32-7095-4848-8418-2D28C06105DB}">
   <dimension ref="B2:C5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="2" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>40</v>
       </c>
@@ -2781,7 +2563,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="5" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B5">
         <f>AVERAGE(0.6,0.75)</f>
         <v>0.67500000000000004</v>
@@ -2797,14 +2579,14 @@
   <sheetPr>
     <tabColor theme="8" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:AI13"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:AI11"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="30.1796875" customWidth="1"/>
-    <col min="2" max="2" width="9.453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.140625" customWidth="1"/>
+    <col min="2" max="2" width="9.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>52</v>
       </c>
@@ -2911,7 +2693,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>42</v>
       </c>
@@ -3052,7 +2834,7 @@
         <v>1.2899679340357322</v>
       </c>
     </row>
-    <row r="3" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>43</v>
       </c>
@@ -3159,7 +2941,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>44</v>
       </c>
@@ -3266,7 +3048,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>45</v>
       </c>
@@ -3373,7 +3155,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>46</v>
       </c>
@@ -3480,7 +3262,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>47</v>
       </c>
@@ -3587,7 +3369,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>48</v>
       </c>
@@ -3694,7 +3476,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>49</v>
       </c>
@@ -3801,7 +3583,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>50</v>
       </c>
@@ -3908,7 +3690,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>51</v>
       </c>
@@ -4012,220 +3794,6 @@
         <v>0</v>
       </c>
       <c r="AI11" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>55</v>
-      </c>
-      <c r="B12" s="12">
-        <v>0</v>
-      </c>
-      <c r="C12" s="12">
-        <v>0</v>
-      </c>
-      <c r="D12" s="12">
-        <v>0</v>
-      </c>
-      <c r="E12" s="12">
-        <v>0</v>
-      </c>
-      <c r="F12" s="12">
-        <v>0</v>
-      </c>
-      <c r="G12" s="12">
-        <v>0</v>
-      </c>
-      <c r="H12" s="12">
-        <v>0</v>
-      </c>
-      <c r="I12" s="12">
-        <v>0</v>
-      </c>
-      <c r="J12" s="12">
-        <v>0</v>
-      </c>
-      <c r="K12" s="12">
-        <v>0</v>
-      </c>
-      <c r="L12" s="12">
-        <v>0</v>
-      </c>
-      <c r="M12" s="12">
-        <v>0</v>
-      </c>
-      <c r="N12" s="12">
-        <v>0</v>
-      </c>
-      <c r="O12" s="12">
-        <v>0</v>
-      </c>
-      <c r="P12" s="12">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="12">
-        <v>0</v>
-      </c>
-      <c r="R12" s="12">
-        <v>0</v>
-      </c>
-      <c r="S12" s="12">
-        <v>0</v>
-      </c>
-      <c r="T12" s="12">
-        <v>0</v>
-      </c>
-      <c r="U12" s="12">
-        <v>0</v>
-      </c>
-      <c r="V12" s="12">
-        <v>0</v>
-      </c>
-      <c r="W12" s="12">
-        <v>0</v>
-      </c>
-      <c r="X12" s="12">
-        <v>0</v>
-      </c>
-      <c r="Y12" s="12">
-        <v>0</v>
-      </c>
-      <c r="Z12" s="12">
-        <v>0</v>
-      </c>
-      <c r="AA12" s="12">
-        <v>0</v>
-      </c>
-      <c r="AB12" s="12">
-        <v>0</v>
-      </c>
-      <c r="AC12" s="12">
-        <v>0</v>
-      </c>
-      <c r="AD12" s="12">
-        <v>0</v>
-      </c>
-      <c r="AE12" s="12">
-        <v>0</v>
-      </c>
-      <c r="AF12" s="12">
-        <v>0</v>
-      </c>
-      <c r="AG12" s="12">
-        <v>0</v>
-      </c>
-      <c r="AH12" s="12">
-        <v>0</v>
-      </c>
-      <c r="AI12" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>56</v>
-      </c>
-      <c r="B13" s="12">
-        <v>0</v>
-      </c>
-      <c r="C13" s="12">
-        <v>0</v>
-      </c>
-      <c r="D13" s="12">
-        <v>0</v>
-      </c>
-      <c r="E13" s="12">
-        <v>0</v>
-      </c>
-      <c r="F13" s="12">
-        <v>0</v>
-      </c>
-      <c r="G13" s="12">
-        <v>0</v>
-      </c>
-      <c r="H13" s="12">
-        <v>0</v>
-      </c>
-      <c r="I13" s="12">
-        <v>0</v>
-      </c>
-      <c r="J13" s="12">
-        <v>0</v>
-      </c>
-      <c r="K13" s="12">
-        <v>0</v>
-      </c>
-      <c r="L13" s="12">
-        <v>0</v>
-      </c>
-      <c r="M13" s="12">
-        <v>0</v>
-      </c>
-      <c r="N13" s="12">
-        <v>0</v>
-      </c>
-      <c r="O13" s="12">
-        <v>0</v>
-      </c>
-      <c r="P13" s="12">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="12">
-        <v>0</v>
-      </c>
-      <c r="R13" s="12">
-        <v>0</v>
-      </c>
-      <c r="S13" s="12">
-        <v>0</v>
-      </c>
-      <c r="T13" s="12">
-        <v>0</v>
-      </c>
-      <c r="U13" s="12">
-        <v>0</v>
-      </c>
-      <c r="V13" s="12">
-        <v>0</v>
-      </c>
-      <c r="W13" s="12">
-        <v>0</v>
-      </c>
-      <c r="X13" s="12">
-        <v>0</v>
-      </c>
-      <c r="Y13" s="12">
-        <v>0</v>
-      </c>
-      <c r="Z13" s="12">
-        <v>0</v>
-      </c>
-      <c r="AA13" s="12">
-        <v>0</v>
-      </c>
-      <c r="AB13" s="12">
-        <v>0</v>
-      </c>
-      <c r="AC13" s="12">
-        <v>0</v>
-      </c>
-      <c r="AD13" s="12">
-        <v>0</v>
-      </c>
-      <c r="AE13" s="12">
-        <v>0</v>
-      </c>
-      <c r="AF13" s="12">
-        <v>0</v>
-      </c>
-      <c r="AG13" s="12">
-        <v>0</v>
-      </c>
-      <c r="AH13" s="12">
-        <v>0</v>
-      </c>
-      <c r="AI13" s="12">
         <v>0</v>
       </c>
     </row>
@@ -4239,14 +3807,14 @@
   <sheetPr>
     <tabColor theme="8" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:AI13"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:AI11"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="30.1796875" customWidth="1"/>
-    <col min="2" max="2" width="9.453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.140625" customWidth="1"/>
+    <col min="2" max="2" width="9.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>52</v>
       </c>
@@ -4353,7 +3921,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>42</v>
       </c>
@@ -4494,7 +4062,7 @@
         <v>1.6949152542372881E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>43</v>
       </c>
@@ -4601,7 +4169,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>44</v>
       </c>
@@ -4742,7 +4310,7 @@
         <v>1.3728813559322033</v>
       </c>
     </row>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>45</v>
       </c>
@@ -4849,7 +4417,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>46</v>
       </c>
@@ -4956,7 +4524,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>47</v>
       </c>
@@ -5063,7 +4631,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>48</v>
       </c>
@@ -5170,7 +4738,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>49</v>
       </c>
@@ -5277,7 +4845,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>50</v>
       </c>
@@ -5384,7 +4952,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>51</v>
       </c>
@@ -5488,220 +5056,6 @@
         <v>0</v>
       </c>
       <c r="AI11" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>55</v>
-      </c>
-      <c r="B12" s="12">
-        <v>0</v>
-      </c>
-      <c r="C12" s="12">
-        <v>0</v>
-      </c>
-      <c r="D12" s="12">
-        <v>0</v>
-      </c>
-      <c r="E12" s="12">
-        <v>0</v>
-      </c>
-      <c r="F12" s="12">
-        <v>0</v>
-      </c>
-      <c r="G12" s="12">
-        <v>0</v>
-      </c>
-      <c r="H12" s="12">
-        <v>0</v>
-      </c>
-      <c r="I12" s="12">
-        <v>0</v>
-      </c>
-      <c r="J12" s="12">
-        <v>0</v>
-      </c>
-      <c r="K12" s="12">
-        <v>0</v>
-      </c>
-      <c r="L12" s="12">
-        <v>0</v>
-      </c>
-      <c r="M12" s="12">
-        <v>0</v>
-      </c>
-      <c r="N12" s="12">
-        <v>0</v>
-      </c>
-      <c r="O12" s="12">
-        <v>0</v>
-      </c>
-      <c r="P12" s="12">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="12">
-        <v>0</v>
-      </c>
-      <c r="R12" s="12">
-        <v>0</v>
-      </c>
-      <c r="S12" s="12">
-        <v>0</v>
-      </c>
-      <c r="T12" s="12">
-        <v>0</v>
-      </c>
-      <c r="U12" s="12">
-        <v>0</v>
-      </c>
-      <c r="V12" s="12">
-        <v>0</v>
-      </c>
-      <c r="W12" s="12">
-        <v>0</v>
-      </c>
-      <c r="X12" s="12">
-        <v>0</v>
-      </c>
-      <c r="Y12" s="12">
-        <v>0</v>
-      </c>
-      <c r="Z12" s="12">
-        <v>0</v>
-      </c>
-      <c r="AA12" s="12">
-        <v>0</v>
-      </c>
-      <c r="AB12" s="12">
-        <v>0</v>
-      </c>
-      <c r="AC12" s="12">
-        <v>0</v>
-      </c>
-      <c r="AD12" s="12">
-        <v>0</v>
-      </c>
-      <c r="AE12" s="12">
-        <v>0</v>
-      </c>
-      <c r="AF12" s="12">
-        <v>0</v>
-      </c>
-      <c r="AG12" s="12">
-        <v>0</v>
-      </c>
-      <c r="AH12" s="12">
-        <v>0</v>
-      </c>
-      <c r="AI12" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>56</v>
-      </c>
-      <c r="B13" s="12">
-        <v>0</v>
-      </c>
-      <c r="C13" s="12">
-        <v>0</v>
-      </c>
-      <c r="D13" s="12">
-        <v>0</v>
-      </c>
-      <c r="E13" s="12">
-        <v>0</v>
-      </c>
-      <c r="F13" s="12">
-        <v>0</v>
-      </c>
-      <c r="G13" s="12">
-        <v>0</v>
-      </c>
-      <c r="H13" s="12">
-        <v>0</v>
-      </c>
-      <c r="I13" s="12">
-        <v>0</v>
-      </c>
-      <c r="J13" s="12">
-        <v>0</v>
-      </c>
-      <c r="K13" s="12">
-        <v>0</v>
-      </c>
-      <c r="L13" s="12">
-        <v>0</v>
-      </c>
-      <c r="M13" s="12">
-        <v>0</v>
-      </c>
-      <c r="N13" s="12">
-        <v>0</v>
-      </c>
-      <c r="O13" s="12">
-        <v>0</v>
-      </c>
-      <c r="P13" s="12">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="12">
-        <v>0</v>
-      </c>
-      <c r="R13" s="12">
-        <v>0</v>
-      </c>
-      <c r="S13" s="12">
-        <v>0</v>
-      </c>
-      <c r="T13" s="12">
-        <v>0</v>
-      </c>
-      <c r="U13" s="12">
-        <v>0</v>
-      </c>
-      <c r="V13" s="12">
-        <v>0</v>
-      </c>
-      <c r="W13" s="12">
-        <v>0</v>
-      </c>
-      <c r="X13" s="12">
-        <v>0</v>
-      </c>
-      <c r="Y13" s="12">
-        <v>0</v>
-      </c>
-      <c r="Z13" s="12">
-        <v>0</v>
-      </c>
-      <c r="AA13" s="12">
-        <v>0</v>
-      </c>
-      <c r="AB13" s="12">
-        <v>0</v>
-      </c>
-      <c r="AC13" s="12">
-        <v>0</v>
-      </c>
-      <c r="AD13" s="12">
-        <v>0</v>
-      </c>
-      <c r="AE13" s="12">
-        <v>0</v>
-      </c>
-      <c r="AF13" s="12">
-        <v>0</v>
-      </c>
-      <c r="AG13" s="12">
-        <v>0</v>
-      </c>
-      <c r="AH13" s="12">
-        <v>0</v>
-      </c>
-      <c r="AI13" s="12">
         <v>0</v>
       </c>
     </row>
@@ -5715,14 +5069,14 @@
   <sheetPr>
     <tabColor theme="8" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:AI13"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:AI11"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="30.1796875" customWidth="1"/>
-    <col min="2" max="2" width="9.453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.140625" customWidth="1"/>
+    <col min="2" max="2" width="9.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>52</v>
       </c>
@@ -5829,7 +5183,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>42</v>
       </c>
@@ -5970,255 +5324,255 @@
         <v>5.0847457627118647E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>43</v>
       </c>
       <c r="B3" s="12">
-        <v>0</v>
+        <f>201/118</f>
+        <v>1.7033898305084745</v>
       </c>
       <c r="C3" s="12">
-        <v>0</v>
+        <f>B3</f>
+        <v>1.7033898305084745</v>
       </c>
       <c r="D3" s="12">
-        <v>0</v>
+        <f t="shared" ref="D3:AI3" si="1">C3</f>
+        <v>1.7033898305084745</v>
       </c>
       <c r="E3" s="12">
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>1.7033898305084745</v>
       </c>
       <c r="F3" s="12">
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>1.7033898305084745</v>
       </c>
       <c r="G3" s="12">
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>1.7033898305084745</v>
       </c>
       <c r="H3" s="12">
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>1.7033898305084745</v>
       </c>
       <c r="I3" s="12">
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>1.7033898305084745</v>
       </c>
       <c r="J3" s="12">
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>1.7033898305084745</v>
       </c>
       <c r="K3" s="12">
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>1.7033898305084745</v>
       </c>
       <c r="L3" s="12">
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>1.7033898305084745</v>
       </c>
       <c r="M3" s="12">
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>1.7033898305084745</v>
       </c>
       <c r="N3" s="12">
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>1.7033898305084745</v>
       </c>
       <c r="O3" s="12">
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>1.7033898305084745</v>
       </c>
       <c r="P3" s="12">
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>1.7033898305084745</v>
       </c>
       <c r="Q3" s="12">
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>1.7033898305084745</v>
       </c>
       <c r="R3" s="12">
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>1.7033898305084745</v>
       </c>
       <c r="S3" s="12">
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>1.7033898305084745</v>
       </c>
       <c r="T3" s="12">
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>1.7033898305084745</v>
       </c>
       <c r="U3" s="12">
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>1.7033898305084745</v>
       </c>
       <c r="V3" s="12">
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>1.7033898305084745</v>
       </c>
       <c r="W3" s="12">
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>1.7033898305084745</v>
       </c>
       <c r="X3" s="12">
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>1.7033898305084745</v>
       </c>
       <c r="Y3" s="12">
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>1.7033898305084745</v>
       </c>
       <c r="Z3" s="12">
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>1.7033898305084745</v>
       </c>
       <c r="AA3" s="12">
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>1.7033898305084745</v>
       </c>
       <c r="AB3" s="12">
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>1.7033898305084745</v>
       </c>
       <c r="AC3" s="12">
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>1.7033898305084745</v>
       </c>
       <c r="AD3" s="12">
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>1.7033898305084745</v>
       </c>
       <c r="AE3" s="12">
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>1.7033898305084745</v>
       </c>
       <c r="AF3" s="12">
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>1.7033898305084745</v>
       </c>
       <c r="AG3" s="12">
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>1.7033898305084745</v>
       </c>
       <c r="AH3" s="12">
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>1.7033898305084745</v>
       </c>
       <c r="AI3" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:35" x14ac:dyDescent="0.35">
+        <f t="shared" si="1"/>
+        <v>1.7033898305084745</v>
+      </c>
+    </row>
+    <row r="4" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>44</v>
       </c>
       <c r="B4" s="12">
-        <f>201/118</f>
-        <v>1.7033898305084745</v>
+        <v>0</v>
       </c>
       <c r="C4" s="12">
-        <f>B4</f>
-        <v>1.7033898305084745</v>
+        <v>0</v>
       </c>
       <c r="D4" s="12">
-        <f t="shared" ref="D4:O4" si="1">C4</f>
-        <v>1.7033898305084745</v>
+        <v>0</v>
       </c>
       <c r="E4" s="12">
-        <f t="shared" si="1"/>
-        <v>1.7033898305084745</v>
+        <v>0</v>
       </c>
       <c r="F4" s="12">
-        <f t="shared" si="1"/>
-        <v>1.7033898305084745</v>
+        <v>0</v>
       </c>
       <c r="G4" s="12">
-        <f t="shared" si="1"/>
-        <v>1.7033898305084745</v>
+        <v>0</v>
       </c>
       <c r="H4" s="12">
-        <f t="shared" si="1"/>
-        <v>1.7033898305084745</v>
+        <v>0</v>
       </c>
       <c r="I4" s="12">
-        <f t="shared" si="1"/>
-        <v>1.7033898305084745</v>
+        <v>0</v>
       </c>
       <c r="J4" s="12">
-        <f t="shared" si="1"/>
-        <v>1.7033898305084745</v>
+        <v>0</v>
       </c>
       <c r="K4" s="12">
-        <f t="shared" si="1"/>
-        <v>1.7033898305084745</v>
+        <v>0</v>
       </c>
       <c r="L4" s="12">
-        <f t="shared" si="1"/>
-        <v>1.7033898305084745</v>
+        <v>0</v>
       </c>
       <c r="M4" s="12">
-        <f t="shared" si="1"/>
-        <v>1.7033898305084745</v>
+        <v>0</v>
       </c>
       <c r="N4" s="12">
-        <f t="shared" si="1"/>
-        <v>1.7033898305084745</v>
+        <v>0</v>
       </c>
       <c r="O4" s="12">
-        <f t="shared" si="1"/>
-        <v>1.7033898305084745</v>
+        <v>0</v>
       </c>
       <c r="P4" s="13">
-        <f t="shared" ref="P4:AI4" si="2">O4</f>
-        <v>1.7033898305084745</v>
+        <v>0</v>
       </c>
       <c r="Q4" s="12">
-        <f t="shared" si="2"/>
-        <v>1.7033898305084745</v>
+        <v>0</v>
       </c>
       <c r="R4" s="12">
-        <f t="shared" si="2"/>
-        <v>1.7033898305084745</v>
+        <v>0</v>
       </c>
       <c r="S4" s="12">
-        <f t="shared" si="2"/>
-        <v>1.7033898305084745</v>
+        <v>0</v>
       </c>
       <c r="T4" s="12">
-        <f t="shared" si="2"/>
-        <v>1.7033898305084745</v>
+        <v>0</v>
       </c>
       <c r="U4" s="12">
-        <f t="shared" si="2"/>
-        <v>1.7033898305084745</v>
+        <v>0</v>
       </c>
       <c r="V4" s="12">
-        <f t="shared" si="2"/>
-        <v>1.7033898305084745</v>
+        <v>0</v>
       </c>
       <c r="W4" s="12">
-        <f t="shared" si="2"/>
-        <v>1.7033898305084745</v>
+        <v>0</v>
       </c>
       <c r="X4" s="12">
-        <f t="shared" si="2"/>
-        <v>1.7033898305084745</v>
+        <v>0</v>
       </c>
       <c r="Y4" s="12">
-        <f t="shared" si="2"/>
-        <v>1.7033898305084745</v>
+        <v>0</v>
       </c>
       <c r="Z4" s="12">
-        <f t="shared" si="2"/>
-        <v>1.7033898305084745</v>
+        <v>0</v>
       </c>
       <c r="AA4" s="12">
-        <f t="shared" si="2"/>
-        <v>1.7033898305084745</v>
+        <v>0</v>
       </c>
       <c r="AB4" s="12">
-        <f t="shared" si="2"/>
-        <v>1.7033898305084745</v>
+        <v>0</v>
       </c>
       <c r="AC4" s="12">
-        <f t="shared" si="2"/>
-        <v>1.7033898305084745</v>
+        <v>0</v>
       </c>
       <c r="AD4" s="12">
-        <f t="shared" si="2"/>
-        <v>1.7033898305084745</v>
+        <v>0</v>
       </c>
       <c r="AE4" s="12">
-        <f t="shared" si="2"/>
-        <v>1.7033898305084745</v>
+        <v>0</v>
       </c>
       <c r="AF4" s="12">
-        <f t="shared" si="2"/>
-        <v>1.7033898305084745</v>
+        <v>0</v>
       </c>
       <c r="AG4" s="12">
-        <f t="shared" si="2"/>
-        <v>1.7033898305084745</v>
+        <v>0</v>
       </c>
       <c r="AH4" s="12">
-        <f t="shared" si="2"/>
-        <v>1.7033898305084745</v>
+        <v>0</v>
       </c>
       <c r="AI4" s="12">
-        <f t="shared" si="2"/>
-        <v>1.7033898305084745</v>
-      </c>
-    </row>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>45</v>
       </c>
@@ -6325,7 +5679,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>46</v>
       </c>
@@ -6432,7 +5786,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>47</v>
       </c>
@@ -6539,7 +5893,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>48</v>
       </c>
@@ -6646,7 +6000,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>49</v>
       </c>
@@ -6753,7 +6107,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>50</v>
       </c>
@@ -6860,7 +6214,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>51</v>
       </c>
@@ -6964,220 +6318,6 @@
         <v>0</v>
       </c>
       <c r="AI11" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>55</v>
-      </c>
-      <c r="B12" s="12">
-        <v>0</v>
-      </c>
-      <c r="C12" s="12">
-        <v>0</v>
-      </c>
-      <c r="D12" s="12">
-        <v>0</v>
-      </c>
-      <c r="E12" s="12">
-        <v>0</v>
-      </c>
-      <c r="F12" s="12">
-        <v>0</v>
-      </c>
-      <c r="G12" s="12">
-        <v>0</v>
-      </c>
-      <c r="H12" s="12">
-        <v>0</v>
-      </c>
-      <c r="I12" s="12">
-        <v>0</v>
-      </c>
-      <c r="J12" s="12">
-        <v>0</v>
-      </c>
-      <c r="K12" s="12">
-        <v>0</v>
-      </c>
-      <c r="L12" s="12">
-        <v>0</v>
-      </c>
-      <c r="M12" s="12">
-        <v>0</v>
-      </c>
-      <c r="N12" s="12">
-        <v>0</v>
-      </c>
-      <c r="O12" s="12">
-        <v>0</v>
-      </c>
-      <c r="P12" s="12">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="12">
-        <v>0</v>
-      </c>
-      <c r="R12" s="12">
-        <v>0</v>
-      </c>
-      <c r="S12" s="12">
-        <v>0</v>
-      </c>
-      <c r="T12" s="12">
-        <v>0</v>
-      </c>
-      <c r="U12" s="12">
-        <v>0</v>
-      </c>
-      <c r="V12" s="12">
-        <v>0</v>
-      </c>
-      <c r="W12" s="12">
-        <v>0</v>
-      </c>
-      <c r="X12" s="12">
-        <v>0</v>
-      </c>
-      <c r="Y12" s="12">
-        <v>0</v>
-      </c>
-      <c r="Z12" s="12">
-        <v>0</v>
-      </c>
-      <c r="AA12" s="12">
-        <v>0</v>
-      </c>
-      <c r="AB12" s="12">
-        <v>0</v>
-      </c>
-      <c r="AC12" s="12">
-        <v>0</v>
-      </c>
-      <c r="AD12" s="12">
-        <v>0</v>
-      </c>
-      <c r="AE12" s="12">
-        <v>0</v>
-      </c>
-      <c r="AF12" s="12">
-        <v>0</v>
-      </c>
-      <c r="AG12" s="12">
-        <v>0</v>
-      </c>
-      <c r="AH12" s="12">
-        <v>0</v>
-      </c>
-      <c r="AI12" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>56</v>
-      </c>
-      <c r="B13" s="12">
-        <v>0</v>
-      </c>
-      <c r="C13" s="12">
-        <v>0</v>
-      </c>
-      <c r="D13" s="12">
-        <v>0</v>
-      </c>
-      <c r="E13" s="12">
-        <v>0</v>
-      </c>
-      <c r="F13" s="12">
-        <v>0</v>
-      </c>
-      <c r="G13" s="12">
-        <v>0</v>
-      </c>
-      <c r="H13" s="12">
-        <v>0</v>
-      </c>
-      <c r="I13" s="12">
-        <v>0</v>
-      </c>
-      <c r="J13" s="12">
-        <v>0</v>
-      </c>
-      <c r="K13" s="12">
-        <v>0</v>
-      </c>
-      <c r="L13" s="12">
-        <v>0</v>
-      </c>
-      <c r="M13" s="12">
-        <v>0</v>
-      </c>
-      <c r="N13" s="12">
-        <v>0</v>
-      </c>
-      <c r="O13" s="12">
-        <v>0</v>
-      </c>
-      <c r="P13" s="12">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="12">
-        <v>0</v>
-      </c>
-      <c r="R13" s="12">
-        <v>0</v>
-      </c>
-      <c r="S13" s="12">
-        <v>0</v>
-      </c>
-      <c r="T13" s="12">
-        <v>0</v>
-      </c>
-      <c r="U13" s="12">
-        <v>0</v>
-      </c>
-      <c r="V13" s="12">
-        <v>0</v>
-      </c>
-      <c r="W13" s="12">
-        <v>0</v>
-      </c>
-      <c r="X13" s="12">
-        <v>0</v>
-      </c>
-      <c r="Y13" s="12">
-        <v>0</v>
-      </c>
-      <c r="Z13" s="12">
-        <v>0</v>
-      </c>
-      <c r="AA13" s="12">
-        <v>0</v>
-      </c>
-      <c r="AB13" s="12">
-        <v>0</v>
-      </c>
-      <c r="AC13" s="12">
-        <v>0</v>
-      </c>
-      <c r="AD13" s="12">
-        <v>0</v>
-      </c>
-      <c r="AE13" s="12">
-        <v>0</v>
-      </c>
-      <c r="AF13" s="12">
-        <v>0</v>
-      </c>
-      <c r="AG13" s="12">
-        <v>0</v>
-      </c>
-      <c r="AH13" s="12">
-        <v>0</v>
-      </c>
-      <c r="AI13" s="12">
         <v>0</v>
       </c>
     </row>
@@ -7191,14 +6331,14 @@
   <sheetPr>
     <tabColor theme="8" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:AI13"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:AI11"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="30.1796875" customWidth="1"/>
-    <col min="2" max="2" width="9.453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.140625" customWidth="1"/>
+    <col min="2" max="2" width="9.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>52</v>
       </c>
@@ -7305,7 +6445,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>42</v>
       </c>
@@ -7446,7 +6586,7 @@
         <v>2.5423728813559324E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>43</v>
       </c>
@@ -7553,7 +6693,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>44</v>
       </c>
@@ -7694,7 +6834,7 @@
         <v>5.0847457627118647E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>45</v>
       </c>
@@ -7835,7 +6975,7 @@
         <v>2.0847457627118646</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>46</v>
       </c>
@@ -7942,7 +7082,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>47</v>
       </c>
@@ -8049,7 +7189,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>48</v>
       </c>
@@ -8156,7 +7296,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>49</v>
       </c>
@@ -8263,7 +7403,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>50</v>
       </c>
@@ -8370,7 +7510,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>51</v>
       </c>
@@ -8474,220 +7614,6 @@
         <v>0</v>
       </c>
       <c r="AI11" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>55</v>
-      </c>
-      <c r="B12" s="12">
-        <v>0</v>
-      </c>
-      <c r="C12" s="12">
-        <v>0</v>
-      </c>
-      <c r="D12" s="12">
-        <v>0</v>
-      </c>
-      <c r="E12" s="12">
-        <v>0</v>
-      </c>
-      <c r="F12" s="12">
-        <v>0</v>
-      </c>
-      <c r="G12" s="12">
-        <v>0</v>
-      </c>
-      <c r="H12" s="12">
-        <v>0</v>
-      </c>
-      <c r="I12" s="12">
-        <v>0</v>
-      </c>
-      <c r="J12" s="12">
-        <v>0</v>
-      </c>
-      <c r="K12" s="12">
-        <v>0</v>
-      </c>
-      <c r="L12" s="12">
-        <v>0</v>
-      </c>
-      <c r="M12" s="12">
-        <v>0</v>
-      </c>
-      <c r="N12" s="12">
-        <v>0</v>
-      </c>
-      <c r="O12" s="12">
-        <v>0</v>
-      </c>
-      <c r="P12" s="12">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="12">
-        <v>0</v>
-      </c>
-      <c r="R12" s="12">
-        <v>0</v>
-      </c>
-      <c r="S12" s="12">
-        <v>0</v>
-      </c>
-      <c r="T12" s="12">
-        <v>0</v>
-      </c>
-      <c r="U12" s="12">
-        <v>0</v>
-      </c>
-      <c r="V12" s="12">
-        <v>0</v>
-      </c>
-      <c r="W12" s="12">
-        <v>0</v>
-      </c>
-      <c r="X12" s="12">
-        <v>0</v>
-      </c>
-      <c r="Y12" s="12">
-        <v>0</v>
-      </c>
-      <c r="Z12" s="12">
-        <v>0</v>
-      </c>
-      <c r="AA12" s="12">
-        <v>0</v>
-      </c>
-      <c r="AB12" s="12">
-        <v>0</v>
-      </c>
-      <c r="AC12" s="12">
-        <v>0</v>
-      </c>
-      <c r="AD12" s="12">
-        <v>0</v>
-      </c>
-      <c r="AE12" s="12">
-        <v>0</v>
-      </c>
-      <c r="AF12" s="12">
-        <v>0</v>
-      </c>
-      <c r="AG12" s="12">
-        <v>0</v>
-      </c>
-      <c r="AH12" s="12">
-        <v>0</v>
-      </c>
-      <c r="AI12" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>56</v>
-      </c>
-      <c r="B13" s="12">
-        <v>0</v>
-      </c>
-      <c r="C13" s="12">
-        <v>0</v>
-      </c>
-      <c r="D13" s="12">
-        <v>0</v>
-      </c>
-      <c r="E13" s="12">
-        <v>0</v>
-      </c>
-      <c r="F13" s="12">
-        <v>0</v>
-      </c>
-      <c r="G13" s="12">
-        <v>0</v>
-      </c>
-      <c r="H13" s="12">
-        <v>0</v>
-      </c>
-      <c r="I13" s="12">
-        <v>0</v>
-      </c>
-      <c r="J13" s="12">
-        <v>0</v>
-      </c>
-      <c r="K13" s="12">
-        <v>0</v>
-      </c>
-      <c r="L13" s="12">
-        <v>0</v>
-      </c>
-      <c r="M13" s="12">
-        <v>0</v>
-      </c>
-      <c r="N13" s="12">
-        <v>0</v>
-      </c>
-      <c r="O13" s="12">
-        <v>0</v>
-      </c>
-      <c r="P13" s="12">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="12">
-        <v>0</v>
-      </c>
-      <c r="R13" s="12">
-        <v>0</v>
-      </c>
-      <c r="S13" s="12">
-        <v>0</v>
-      </c>
-      <c r="T13" s="12">
-        <v>0</v>
-      </c>
-      <c r="U13" s="12">
-        <v>0</v>
-      </c>
-      <c r="V13" s="12">
-        <v>0</v>
-      </c>
-      <c r="W13" s="12">
-        <v>0</v>
-      </c>
-      <c r="X13" s="12">
-        <v>0</v>
-      </c>
-      <c r="Y13" s="12">
-        <v>0</v>
-      </c>
-      <c r="Z13" s="12">
-        <v>0</v>
-      </c>
-      <c r="AA13" s="12">
-        <v>0</v>
-      </c>
-      <c r="AB13" s="12">
-        <v>0</v>
-      </c>
-      <c r="AC13" s="12">
-        <v>0</v>
-      </c>
-      <c r="AD13" s="12">
-        <v>0</v>
-      </c>
-      <c r="AE13" s="12">
-        <v>0</v>
-      </c>
-      <c r="AF13" s="12">
-        <v>0</v>
-      </c>
-      <c r="AG13" s="12">
-        <v>0</v>
-      </c>
-      <c r="AH13" s="12">
-        <v>0</v>
-      </c>
-      <c r="AI13" s="12">
         <v>0</v>
       </c>
     </row>
@@ -8701,14 +7627,14 @@
   <sheetPr>
     <tabColor theme="8" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:AI13"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:AI11"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="30.1796875" customWidth="1"/>
-    <col min="2" max="2" width="9.453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.140625" customWidth="1"/>
+    <col min="2" max="2" width="9.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>52</v>
       </c>
@@ -8815,7 +7741,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>42</v>
       </c>
@@ -8955,7 +7881,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>43</v>
       </c>
@@ -9062,7 +7988,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>44</v>
       </c>
@@ -9202,7 +8128,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>45</v>
       </c>
@@ -9342,7 +8268,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>46</v>
       </c>
@@ -9449,7 +8375,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>47</v>
       </c>
@@ -9556,7 +8482,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>48</v>
       </c>
@@ -9663,7 +8589,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>49</v>
       </c>
@@ -9804,7 +8730,7 @@
         <v>1.4814814814814814</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>50</v>
       </c>
@@ -9911,7 +8837,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>51</v>
       </c>
@@ -10015,220 +8941,6 @@
         <v>0</v>
       </c>
       <c r="AI11" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>55</v>
-      </c>
-      <c r="B12" s="12">
-        <v>0</v>
-      </c>
-      <c r="C12" s="12">
-        <v>0</v>
-      </c>
-      <c r="D12" s="12">
-        <v>0</v>
-      </c>
-      <c r="E12" s="12">
-        <v>0</v>
-      </c>
-      <c r="F12" s="12">
-        <v>0</v>
-      </c>
-      <c r="G12" s="12">
-        <v>0</v>
-      </c>
-      <c r="H12" s="12">
-        <v>0</v>
-      </c>
-      <c r="I12" s="12">
-        <v>0</v>
-      </c>
-      <c r="J12" s="12">
-        <v>0</v>
-      </c>
-      <c r="K12" s="12">
-        <v>0</v>
-      </c>
-      <c r="L12" s="12">
-        <v>0</v>
-      </c>
-      <c r="M12" s="12">
-        <v>0</v>
-      </c>
-      <c r="N12" s="12">
-        <v>0</v>
-      </c>
-      <c r="O12" s="12">
-        <v>0</v>
-      </c>
-      <c r="P12" s="12">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="12">
-        <v>0</v>
-      </c>
-      <c r="R12" s="12">
-        <v>0</v>
-      </c>
-      <c r="S12" s="12">
-        <v>0</v>
-      </c>
-      <c r="T12" s="12">
-        <v>0</v>
-      </c>
-      <c r="U12" s="12">
-        <v>0</v>
-      </c>
-      <c r="V12" s="12">
-        <v>0</v>
-      </c>
-      <c r="W12" s="12">
-        <v>0</v>
-      </c>
-      <c r="X12" s="12">
-        <v>0</v>
-      </c>
-      <c r="Y12" s="12">
-        <v>0</v>
-      </c>
-      <c r="Z12" s="12">
-        <v>0</v>
-      </c>
-      <c r="AA12" s="12">
-        <v>0</v>
-      </c>
-      <c r="AB12" s="12">
-        <v>0</v>
-      </c>
-      <c r="AC12" s="12">
-        <v>0</v>
-      </c>
-      <c r="AD12" s="12">
-        <v>0</v>
-      </c>
-      <c r="AE12" s="12">
-        <v>0</v>
-      </c>
-      <c r="AF12" s="12">
-        <v>0</v>
-      </c>
-      <c r="AG12" s="12">
-        <v>0</v>
-      </c>
-      <c r="AH12" s="12">
-        <v>0</v>
-      </c>
-      <c r="AI12" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>56</v>
-      </c>
-      <c r="B13" s="12">
-        <v>0</v>
-      </c>
-      <c r="C13" s="12">
-        <v>0</v>
-      </c>
-      <c r="D13" s="12">
-        <v>0</v>
-      </c>
-      <c r="E13" s="12">
-        <v>0</v>
-      </c>
-      <c r="F13" s="12">
-        <v>0</v>
-      </c>
-      <c r="G13" s="12">
-        <v>0</v>
-      </c>
-      <c r="H13" s="12">
-        <v>0</v>
-      </c>
-      <c r="I13" s="12">
-        <v>0</v>
-      </c>
-      <c r="J13" s="12">
-        <v>0</v>
-      </c>
-      <c r="K13" s="12">
-        <v>0</v>
-      </c>
-      <c r="L13" s="12">
-        <v>0</v>
-      </c>
-      <c r="M13" s="12">
-        <v>0</v>
-      </c>
-      <c r="N13" s="12">
-        <v>0</v>
-      </c>
-      <c r="O13" s="12">
-        <v>0</v>
-      </c>
-      <c r="P13" s="12">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="12">
-        <v>0</v>
-      </c>
-      <c r="R13" s="12">
-        <v>0</v>
-      </c>
-      <c r="S13" s="12">
-        <v>0</v>
-      </c>
-      <c r="T13" s="12">
-        <v>0</v>
-      </c>
-      <c r="U13" s="12">
-        <v>0</v>
-      </c>
-      <c r="V13" s="12">
-        <v>0</v>
-      </c>
-      <c r="W13" s="12">
-        <v>0</v>
-      </c>
-      <c r="X13" s="12">
-        <v>0</v>
-      </c>
-      <c r="Y13" s="12">
-        <v>0</v>
-      </c>
-      <c r="Z13" s="12">
-        <v>0</v>
-      </c>
-      <c r="AA13" s="12">
-        <v>0</v>
-      </c>
-      <c r="AB13" s="12">
-        <v>0</v>
-      </c>
-      <c r="AC13" s="12">
-        <v>0</v>
-      </c>
-      <c r="AD13" s="12">
-        <v>0</v>
-      </c>
-      <c r="AE13" s="12">
-        <v>0</v>
-      </c>
-      <c r="AF13" s="12">
-        <v>0</v>
-      </c>
-      <c r="AG13" s="12">
-        <v>0</v>
-      </c>
-      <c r="AH13" s="12">
-        <v>0</v>
-      </c>
-      <c r="AI13" s="12">
         <v>0</v>
       </c>
     </row>
@@ -10242,14 +8954,14 @@
   <sheetPr>
     <tabColor theme="8" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:AI13"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:AI11"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="30.1796875" customWidth="1"/>
-    <col min="2" max="2" width="9.453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.140625" customWidth="1"/>
+    <col min="2" max="2" width="9.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>52</v>
       </c>
@@ -10356,7 +9068,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>42</v>
       </c>
@@ -10497,7 +9209,7 @@
         <v>1.2899679340357322</v>
       </c>
     </row>
-    <row r="3" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>43</v>
       </c>
@@ -10604,7 +9316,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>44</v>
       </c>
@@ -10744,7 +9456,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>45</v>
       </c>
@@ -10884,7 +9596,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>46</v>
       </c>
@@ -10991,7 +9703,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>47</v>
       </c>
@@ -11098,7 +9810,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>48</v>
       </c>
@@ -11205,7 +9917,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>49</v>
       </c>
@@ -11345,7 +10057,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>50</v>
       </c>
@@ -11452,7 +10164,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>51</v>
       </c>
@@ -11556,220 +10268,6 @@
         <v>0</v>
       </c>
       <c r="AI11" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>55</v>
-      </c>
-      <c r="B12" s="12">
-        <v>0</v>
-      </c>
-      <c r="C12" s="12">
-        <v>0</v>
-      </c>
-      <c r="D12" s="12">
-        <v>0</v>
-      </c>
-      <c r="E12" s="12">
-        <v>0</v>
-      </c>
-      <c r="F12" s="12">
-        <v>0</v>
-      </c>
-      <c r="G12" s="12">
-        <v>0</v>
-      </c>
-      <c r="H12" s="12">
-        <v>0</v>
-      </c>
-      <c r="I12" s="12">
-        <v>0</v>
-      </c>
-      <c r="J12" s="12">
-        <v>0</v>
-      </c>
-      <c r="K12" s="12">
-        <v>0</v>
-      </c>
-      <c r="L12" s="12">
-        <v>0</v>
-      </c>
-      <c r="M12" s="12">
-        <v>0</v>
-      </c>
-      <c r="N12" s="12">
-        <v>0</v>
-      </c>
-      <c r="O12" s="12">
-        <v>0</v>
-      </c>
-      <c r="P12" s="12">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="12">
-        <v>0</v>
-      </c>
-      <c r="R12" s="12">
-        <v>0</v>
-      </c>
-      <c r="S12" s="12">
-        <v>0</v>
-      </c>
-      <c r="T12" s="12">
-        <v>0</v>
-      </c>
-      <c r="U12" s="12">
-        <v>0</v>
-      </c>
-      <c r="V12" s="12">
-        <v>0</v>
-      </c>
-      <c r="W12" s="12">
-        <v>0</v>
-      </c>
-      <c r="X12" s="12">
-        <v>0</v>
-      </c>
-      <c r="Y12" s="12">
-        <v>0</v>
-      </c>
-      <c r="Z12" s="12">
-        <v>0</v>
-      </c>
-      <c r="AA12" s="12">
-        <v>0</v>
-      </c>
-      <c r="AB12" s="12">
-        <v>0</v>
-      </c>
-      <c r="AC12" s="12">
-        <v>0</v>
-      </c>
-      <c r="AD12" s="12">
-        <v>0</v>
-      </c>
-      <c r="AE12" s="12">
-        <v>0</v>
-      </c>
-      <c r="AF12" s="12">
-        <v>0</v>
-      </c>
-      <c r="AG12" s="12">
-        <v>0</v>
-      </c>
-      <c r="AH12" s="12">
-        <v>0</v>
-      </c>
-      <c r="AI12" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>56</v>
-      </c>
-      <c r="B13" s="12">
-        <v>0</v>
-      </c>
-      <c r="C13" s="12">
-        <v>0</v>
-      </c>
-      <c r="D13" s="12">
-        <v>0</v>
-      </c>
-      <c r="E13" s="12">
-        <v>0</v>
-      </c>
-      <c r="F13" s="12">
-        <v>0</v>
-      </c>
-      <c r="G13" s="12">
-        <v>0</v>
-      </c>
-      <c r="H13" s="12">
-        <v>0</v>
-      </c>
-      <c r="I13" s="12">
-        <v>0</v>
-      </c>
-      <c r="J13" s="12">
-        <v>0</v>
-      </c>
-      <c r="K13" s="12">
-        <v>0</v>
-      </c>
-      <c r="L13" s="12">
-        <v>0</v>
-      </c>
-      <c r="M13" s="12">
-        <v>0</v>
-      </c>
-      <c r="N13" s="12">
-        <v>0</v>
-      </c>
-      <c r="O13" s="12">
-        <v>0</v>
-      </c>
-      <c r="P13" s="12">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="12">
-        <v>0</v>
-      </c>
-      <c r="R13" s="12">
-        <v>0</v>
-      </c>
-      <c r="S13" s="12">
-        <v>0</v>
-      </c>
-      <c r="T13" s="12">
-        <v>0</v>
-      </c>
-      <c r="U13" s="12">
-        <v>0</v>
-      </c>
-      <c r="V13" s="12">
-        <v>0</v>
-      </c>
-      <c r="W13" s="12">
-        <v>0</v>
-      </c>
-      <c r="X13" s="12">
-        <v>0</v>
-      </c>
-      <c r="Y13" s="12">
-        <v>0</v>
-      </c>
-      <c r="Z13" s="12">
-        <v>0</v>
-      </c>
-      <c r="AA13" s="12">
-        <v>0</v>
-      </c>
-      <c r="AB13" s="12">
-        <v>0</v>
-      </c>
-      <c r="AC13" s="12">
-        <v>0</v>
-      </c>
-      <c r="AD13" s="12">
-        <v>0</v>
-      </c>
-      <c r="AE13" s="12">
-        <v>0</v>
-      </c>
-      <c r="AF13" s="12">
-        <v>0</v>
-      </c>
-      <c r="AG13" s="12">
-        <v>0</v>
-      </c>
-      <c r="AH13" s="12">
-        <v>0</v>
-      </c>
-      <c r="AI13" s="12">
         <v>0</v>
       </c>
     </row>
